--- a/forms/app/chv_youth_peer_education.xlsx
+++ b/forms/app/chv_youth_peer_education.xlsx
@@ -1,23 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20379"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6F62DC-16EE-4C5C-8134-89F1A5FB1E33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16385" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -27,589 +22,141 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="214">
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>label::en</t>
-  </si>
-  <si>
-    <t>label::sw</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>read_only</t>
-  </si>
-  <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>hint::en</t>
-  </si>
-  <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
-    <t>media::image::en</t>
-  </si>
-  <si>
-    <t>media::image::sw</t>
-  </si>
-  <si>
-    <t>media::audio::en</t>
-  </si>
-  <si>
-    <t>media::audio::sw</t>
-  </si>
-  <si>
-    <t>begin group</t>
-  </si>
-  <si>
-    <t>inputs</t>
-  </si>
-  <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>contact_id</t>
-  </si>
-  <si>
-    <t>Contact ID of the logged in user</t>
-  </si>
-  <si>
-    <t>facility_id</t>
-  </si>
-  <si>
-    <t>Facility ID for the parent user</t>
-  </si>
-  <si>
-    <t>Name of the logged in user</t>
-  </si>
-  <si>
-    <t>end group</t>
-  </si>
-  <si>
-    <t>contact</t>
-  </si>
-  <si>
-    <t>db:person</t>
-  </si>
-  <si>
-    <t>_id</t>
-  </si>
-  <si>
-    <t>db-object</t>
-  </si>
-  <si>
-    <t>start</t>
-  </si>
-  <si>
-    <t>end</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="217">
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relevant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">appearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">read_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint_message::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">constraint_message::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice_filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hint::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hint::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repeat_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media::image::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media::image::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media::audio::en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media::audio::sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">begin group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO_LABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">facility_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facility ID for the parent user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of the logged in user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">db:person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">db-object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end</t>
   </si>
   <si>
     <t xml:space="preserve">end group </t>
   </si>
   <si>
-    <t>meeting_info</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>peer_name</t>
-  </si>
-  <si>
-    <t>Jina la M/rika</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>shehia</t>
-  </si>
-  <si>
-    <t>Jina la shehia</t>
-  </si>
-  <si>
-    <t>meeting_topic</t>
-  </si>
-  <si>
-    <t>Mada ya Mkutano</t>
-  </si>
-  <si>
-    <t>age_group</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>.&gt;=0</t>
-  </si>
-  <si>
-    <t>idadi haiwezi kuwa chini ya 0</t>
-  </si>
-  <si>
-    <t>male_registered</t>
-  </si>
-  <si>
-    <t>female_registered</t>
-  </si>
-  <si>
-    <t>calculate</t>
-  </si>
-  <si>
-    <t>male_attended</t>
-  </si>
-  <si>
-    <t>female_attended</t>
-  </si>
-  <si>
-    <t>total_attended</t>
-  </si>
-  <si>
-    <t>meeting_challenges</t>
-  </si>
-  <si>
-    <t>Changamoto zilizojitokeza katika mkutano wa kikundi</t>
-  </si>
-  <si>
-    <t>referral_info</t>
-  </si>
-  <si>
-    <t>select_one yes_no</t>
-  </si>
-  <si>
-    <t>has_given_referral_this_month</t>
-  </si>
-  <si>
-    <t>Je umewahi kutoa rufaa kwa kijana ndani ya mwezi huu?</t>
-  </si>
-  <si>
-    <t>${has_given_referral_this_month}=”yes”</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> referral_received_per_month</t>
-  </si>
-  <si>
-    <t>Referral count should be greater or equal to 0</t>
-  </si>
-  <si>
-    <t>facility_referral_count</t>
-  </si>
-  <si>
-    <t>parental_referral_count</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>${has_given_referral_this_month}=”no”</t>
-  </si>
-  <si>
-    <t>Msisitize Muelimishe rika na vijana kujenga Utayari na vijana kutoa taarifa juu ya changamoto zinazowakabili</t>
-  </si>
-  <si>
-    <t>list_name</t>
-  </si>
-  <si>
-    <t>yes_no</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Ndiyo</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Hapana</t>
-  </si>
-  <si>
-    <t>health_concerns</t>
-  </si>
-  <si>
-    <t>cleanliness</t>
-  </si>
-  <si>
-    <t>Cleanliness</t>
-  </si>
-  <si>
-    <t>Usafi</t>
-  </si>
-  <si>
-    <t>water</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>Maji</t>
-  </si>
-  <si>
-    <t>environment</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Mazingira</t>
-  </si>
-  <si>
-    <t>age_10_13</t>
-  </si>
-  <si>
-    <t>10-13</t>
-  </si>
-  <si>
-    <t>age_14_16</t>
-  </si>
-  <si>
-    <t>14-16</t>
-  </si>
-  <si>
-    <t>age_17_19</t>
-  </si>
-  <si>
-    <t>17-19</t>
-  </si>
-  <si>
-    <t>form_title</t>
-  </si>
-  <si>
-    <t>form_id</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elimu Rika na Afya Uzazi </t>
-  </si>
-  <si>
-    <t>field-list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meeting topic </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shehia name </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of youth peer educator </t>
-  </si>
-  <si>
     <t xml:space="preserve">begin group </t>
   </si>
   <si>
-    <t xml:space="preserve">age_group </t>
-  </si>
-  <si>
-    <t>youth_count_info</t>
-  </si>
-  <si>
-    <t>Count of youth registered, attended, and not attended</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idadi ya vijana waliosajiliwa, waliyoshirikia na wasiyoshiriki </t>
-  </si>
-  <si>
-    <t xml:space="preserve">select_one age_group </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select the age group </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chagua umri husika </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count of registered male </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count of registered female </t>
-  </si>
-  <si>
-    <t>total_registered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count of male participants </t>
-  </si>
-  <si>
-    <t>Count of female participants</t>
-  </si>
-  <si>
-    <t>Idadi ya wanaume</t>
-  </si>
-  <si>
-    <t>Idadi ya wanawake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Challenges encountered in the group meeting </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rufaa ya vijana </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youth Referral </t>
-  </si>
-  <si>
-    <t xml:space="preserve">field-list </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have you given a referral to a youth in this month? </t>
-  </si>
-  <si>
-    <t>Idadi ya rufaa ulizopokea kwenye mwezi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referrals received this month </t>
-  </si>
-  <si>
-    <t>Kati ya hizo ni rufaa ngapi uliziwasilisha  kituo cha Afya?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Out of those, how many referrals were directed to health facility? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">educate_youth_educator </t>
-  </si>
-  <si>
-    <t>total_absentees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">youth_registered_note </t>
-  </si>
-  <si>
-    <t>youth_participated_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">youth_not_attended_note </t>
-  </si>
-  <si>
-    <t>total_registered_note</t>
-  </si>
-  <si>
-    <t>total_attended_note</t>
-  </si>
-  <si>
-    <t>total_absentees_note</t>
-  </si>
-  <si>
-    <t>female_absentees</t>
-  </si>
-  <si>
-    <t>male_absentees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total youth participants: ${total_attended} </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total youth registered: ${total_registered} </t>
-  </si>
-  <si>
-    <t>number(${male_absentees})+ number(${female_absentees})</t>
-  </si>
-  <si>
-    <t>peer_phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peer Educator phone number </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nambari ya simu ya M/rika </t>
-  </si>
-  <si>
-    <t>Use the following format 0XXXXXXXXX</t>
-  </si>
-  <si>
-    <t>Tumia mfumo huu 0XXXXXXXXX.</t>
-  </si>
-  <si>
-    <t>Male attended cannot be greater than male registered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idadi ya wanaume walioshiriki haiwezi kuwa kubwa kuliko idadi ya waliyosajiliwa </t>
-  </si>
-  <si>
-    <t>Female attended cannot be greater than female registered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idadi ya wanawake walioshiriki haiwezi kuwa kubwa kuliko idadi ya wanawake waliyosajiliwa </t>
-  </si>
-  <si>
-    <t>male_absentees_note</t>
-  </si>
-  <si>
-    <t>female_absentees_note</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Count of male absentees:&lt;/b&gt; ${male_absentees}</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Idadi ya wanaume wasiyohudhuria:&lt;/b&gt; ${male_absentees}</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Count of female absentees:&lt;/b&gt; ${female_absentees}</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Idadi ya wanawake wasiyohudhuria:&lt;/b&gt; ${female_absentees}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Total absentees:&lt;/b&gt; ${total_absentees} </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Jumla wasiyohudhuria:&lt;/b&gt; ${total_absentees} </t>
-  </si>
-  <si>
-    <t>Facility referral should be between 0 and total referrals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idadi ya rufaa za kituo cha afya haiwezi  iwe baina ya 0 na jumla ya idadi za rufaa za mwezi </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> number(${facility_referral_count}) &lt;= number(${referral_received_per_month})  and number(${facility_referral_count})  &gt;= 0</t>
-  </si>
-  <si>
-    <t>number(${male_attended}) &lt;= number(${male_registered}) and number(${male_attended}) &gt;= 0</t>
-  </si>
-  <si>
-    <t>number(${female_attended}) &lt;= number(${female_registered}) and number(${female_attended}) &gt;= 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">. &gt; 0 </t>
-  </si>
-  <si>
-    <t>. &gt; 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of registered male should be greater than 0 </t>
-  </si>
-  <si>
-    <t>Number of registered female should be greater than 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idadi ya wanawake waliosajiliwa iwe zaidi ya 0 </t>
-  </si>
-  <si>
-    <t>Idadi ya wanaume walisajiliwa iwe zaidi ya 0</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>multiline</t>
-  </si>
-  <si>
-    <t>regex(.,'^[0oO][0-9oO]{9}$')</t>
-  </si>
-  <si>
-    <t>parental_referral_count_qn</t>
-  </si>
-  <si>
-    <t>parental_referral_count_answer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${parental_referral_count} </t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Number of youth not attend a the meeting&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Number of youth participated in the meeting&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Number of registered youth in the groups &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Vijana walioshiriki katika mkutano wa kikundi&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Idadi ya vijana wasiohudhuria katika mkutano wa vikundi&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Idadi ya vijana waliosajiliwa katika vikundi&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Jumla waliyoshiriki:&lt;/b&gt; ${total_attended} </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Jumla waliyosajiliwa:&lt;/b&gt; ${total_registered} </t>
-  </si>
-  <si>
-    <t>if(${male_registered}="" or ${male_registered} &lt;= 0  or ${female_registered} = "" or ${female_registered} &lt;= 0 , 0,number(${male_registered}) + number(${female_registered}))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${male_attended}="" or ${male_attended} &lt; 0  or ${female_attended} = "" or ${female_attended} &lt;= 0 , 0,number(${male_attended}) + number(${female_attended}))
-</t>
-  </si>
-  <si>
-    <t>if(${male_registered}="" or ${male_registered} &lt;= 0  or ${male_attended} = "" or ${male_attended} &lt; 0 , 0,number(${male_registered})-number(${male_attended}))</t>
-  </si>
-  <si>
-    <t>if(${female_registered}="" or ${female_registered} &lt;= 0  or ${female_attended} = "" or ${female_attended} &lt; 0 , 0,number(${female_registered})-number(${female_attended}))</t>
-  </si>
-  <si>
-    <t>covid19_intro</t>
+    <t xml:space="preserve">covid19_intro</t>
   </si>
   <si>
     <t xml:space="preserve">Precautionary measures when visiting a client  </t>
   </si>
   <si>
-    <t>Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
-  </si>
-  <si>
-    <t>covid19_intro_note</t>
+    <t xml:space="preserve">Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">covid19_intro_note</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV, you are responsible for making sure that you are providing the community with health education and services while trying to take precautions to stop the transmission of Corona virus to one another. Therefore, make sure you consider the following while you conduct the visits:  
@@ -636,24 +183,409 @@
 </t>
   </si>
   <si>
-    <t>&lt;b&gt;Rufaa ulizoziunganisha kwa Walezi/wazazi wa vijana&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Referrals which were directed to parents/guardians &lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>chv_youth_peer_education</t>
-  </si>
-  <si>
-    <t>if(${referral_received_per_month}="" or ${referral_received_per_month} &lt; 0  or ${facility_referral_count} = "" or ${facility_referral_count} &lt; 0 or 
+    <t xml:space="preserve">meeting_info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">field-list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peer_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of youth peer educator </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jina la M/rika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peer_phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer Educator phone number </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nambari ya simu ya M/rika </t>
+  </si>
+  <si>
+    <t xml:space="preserve">regex(.,'^[0oO][0-9oO]{9}$')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use the following format 0XXXXXXXXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tumia mfumo huu 0XXXXXXXXX.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shehia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shehia name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jina la shehia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visit_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter visit date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingiza tarehe ya mkutano </t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> . &lt;= date-time(decimal-date-time(today()))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting date cannot be in the future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarehe ya mkutano haiwezi kuzidi tarehe ya leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meeting_topic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting topic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mada ya Mkutano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">youth_count_info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count of youth registered, attended, and not attended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idadi ya vijana waliosajiliwa, waliyoshirikia na wasiyoshiriki </t>
+  </si>
+  <si>
+    <t xml:space="preserve">field-list </t>
+  </si>
+  <si>
+    <t xml:space="preserve">select_one age_group </t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_group </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select the age group </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chagua umri husika </t>
+  </si>
+  <si>
+    <t xml:space="preserve">youth_registered_note </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Number of registered youth in the groups &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Idadi ya vijana waliosajiliwa katika vikundi&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">male_registered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count of registered male </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idadi ya wanaume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">. &gt; 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of registered male should be greater than 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idadi ya wanaume walisajiliwa iwe zaidi ya 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">female_registered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count of registered female </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idadi ya wanawake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">. &gt; 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of registered female should be greater than 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idadi ya wanawake waliosajiliwa iwe zaidi ya 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_registered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${male_registered}="" or ${male_registered} &lt;= 0  or ${female_registered} = "" or ${female_registered} &lt;= 0 , 0,number(${male_registered}) + number(${female_registered}))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_registered_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total youth registered: ${total_registered} </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Jumla waliyosajiliwa:&lt;/b&gt; ${total_registered} </t>
+  </si>
+  <si>
+    <t xml:space="preserve">youth_participated_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Number of youth participated in the meeting&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Vijana walioshiriki katika mkutano wa kikundi&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">male_attended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count of male participants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">number(${male_attended}) &lt;= number(${male_registered}) and number(${male_attended}) &gt;= 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male attended cannot be greater than male registered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idadi ya wanaume walioshiriki haiwezi kuwa kubwa kuliko idadi ya waliyosajiliwa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">female_attended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count of female participants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number(${female_attended}) &lt;= number(${female_registered}) and number(${female_attended}) &gt;= 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female attended cannot be greater than female registered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idadi ya wanawake walioshiriki haiwezi kuwa kubwa kuliko idadi ya wanawake waliyosajiliwa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_attended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${male_attended}="" or ${male_attended} &lt; 0  or ${female_attended} = "" or ${female_attended} &lt;= 0 , 0,number(${male_attended}) + number(${female_attended}))
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_attended_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total youth participants: ${total_attended} </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Jumla waliyoshiriki:&lt;/b&gt; ${total_attended} </t>
+  </si>
+  <si>
+    <t xml:space="preserve">youth_not_attended_note </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Number of youth not attend a the meeting&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Idadi ya vijana wasiohudhuria katika mkutano wa vikundi&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">male_absentees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${male_registered}="" or ${male_registered} &lt;= 0  or ${male_attended} = "" or ${male_attended} &lt; 0 , 0,number(${male_registered})-number(${male_attended}))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">female_absentees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${female_registered}="" or ${female_registered} &lt;= 0  or ${female_attended} = "" or ${female_attended} &lt; 0 , 0,number(${female_registered})-number(${female_attended}))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_absentees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number(${male_absentees})+ number(${female_absentees})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">male_absentees_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Count of male absentees:&lt;/b&gt; ${male_absentees}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Idadi ya wanaume wasiyohudhuria:&lt;/b&gt; ${male_absentees}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">female_absentees_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Count of female absentees:&lt;/b&gt; ${female_absentees}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Idadi ya wanawake wasiyohudhuria:&lt;/b&gt; ${female_absentees}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_absentees_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Total absentees:&lt;/b&gt; ${total_absentees} </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Jumla wasiyohudhuria:&lt;/b&gt; ${total_absentees} </t>
+  </si>
+  <si>
+    <t xml:space="preserve">meeting_challenges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenges encountered in the group meeting </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changamoto zilizojitokeza katika mkutano wa kikundi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multiline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">referral_info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youth Referral </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rufaa ya vijana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">select_one yes_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has_given_referral_this_month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have you given a referral to a youth in this month? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je umewahi kutoa rufaa kwa kijana ndani ya mwezi huu?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> referral_received_per_month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referrals given this month </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idadi ya rufaa ulizotoa kwenye mwezi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${has_given_referral_this_month}=”yes”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.&gt;=0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referral count should be greater or equal to 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idadi haiwezi kuwa chini ya 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">facility_referral_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out of those, how many referrals were directed to health facility? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kati ya hizo ni rufaa ngapi uliziwasilisha  kituo cha Afya?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> number(${facility_referral_count}) &lt;= number(${referral_received_per_month})  and number(${facility_referral_count})  &gt;= 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facility referral should be between 0 and total referrals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idadi ya rufaa za kituo cha afya haiwezi  iwe baina ya 0 na jumla ya idadi za rufaa za mwezi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">parental_referral_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if(${referral_received_per_month}="" or ${referral_received_per_month} &lt; 0  or ${facility_referral_count} = "" or ${facility_referral_count} &lt; 0 or 
 number(${referral_received_per_month}) - number(${facility_referral_count}) &lt; 0
  , 0, number(${referral_received_per_month}) - number(${facility_referral_count}) )</t>
   </si>
   <si>
+    <t xml:space="preserve">parental_referral_count_qn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Referrals which were directed to parents/guardians &lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;b&gt;Rufaa ulizoziunganisha kwa Walezi/wazazi wa vijana&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parental_referral_count_answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${parental_referral_count} </t>
+  </si>
+  <si>
+    <t xml:space="preserve">educate_youth_educator </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Msisitize Muelimishe rika na vijana kujenga Utayari na vijana kutoa taarifa juu ya changamoto zinazowakabili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${has_given_referral_this_month}=”no”</t>
+  </si>
+  <si>
     <t xml:space="preserve">chv_attendance </t>
   </si>
   <si>
-    <t>did_chv_attend</t>
+    <t xml:space="preserve">Meeting Attendance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahudhurio ya mkutano </t>
+  </si>
+  <si>
+    <t xml:space="preserve">note_chv_attend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:red;font-style: italic"&gt;To be answered by the CHV &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="display:block;color:red;font-style: italic;padding-left:1em"&gt;Usimsomee, jaza wewe (CHV). &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">did_chv_attend</t>
   </si>
   <si>
     <t xml:space="preserve">Did you attend the meeting? </t>
@@ -662,46 +594,139 @@
     <t xml:space="preserve">Je ulihudhuria mkutano? </t>
   </si>
   <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>visit_date</t>
-  </si>
-  <si>
-    <t>Enter visit date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingiza tarehe ya mkutano </t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> . &lt;= date-time(decimal-date-time(today()))</t>
-  </si>
-  <si>
-    <t>Meeting date cannot be in the future</t>
-  </si>
-  <si>
-    <t>Tarehe ya mkutano haiwezi kuzidi tarehe ya leo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meeting Attendance </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahudhurio ya mkutano </t>
+    <t xml:space="preserve">list_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ndiyo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hapana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">health_concerns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cleanliness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleanliness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usafi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mazingira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_10_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_14_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_17_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">form_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">form_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elimu Rika na Afya Uzazi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chv_youth_peer_education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="@"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -718,31 +743,23 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="Slack-Lato"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1D1C1D"/>
-      <name val="Slack-Lato"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -756,7 +773,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFF8F8F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -767,394 +784,214 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="19">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFF8F8F8"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF1D1C1D"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4472C4"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z107"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Z108"/>
+  <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="23.26953125" customWidth="1"/>
-    <col min="2" max="2" width="29.08984375" customWidth="1"/>
-    <col min="3" max="3" width="78.31640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="72.1328125" customWidth="1"/>
-    <col min="9" max="9" width="59.04296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="47.31640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="74.54296875" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="78.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="72.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="59.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="47.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="74.54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.75" customHeight="1">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1056,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="15.75" customHeight="1">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -1231,8 +1068,8 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="F2" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="G2" s="1"/>
@@ -1249,7 +1086,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:21" ht="15.75" customHeight="1">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1276,7 +1113,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:21" ht="15.75" customHeight="1">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -1303,7 +1140,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:21" ht="15.75" customHeight="1">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
@@ -1330,7 +1167,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:21" ht="15.75" customHeight="1">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1357,7 +1194,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:21" ht="15.75" customHeight="1">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -1382,7 +1219,7 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:21" ht="15.75" customHeight="1">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
@@ -1409,7 +1246,7 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
     </row>
-    <row r="9" spans="1:21" ht="15.75" customHeight="1">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
@@ -1438,7 +1275,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:21" ht="15.75" customHeight="1">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -1463,7 +1300,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:21" ht="15.75" customHeight="1">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -1488,7 +1325,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:21" ht="15.75" customHeight="1">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
@@ -1513,7 +1350,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:21" ht="15.75" customHeight="1">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
@@ -1538,96 +1375,96 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:21" ht="83.4" customHeight="1">
-      <c r="A14" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-    </row>
-    <row r="15" spans="1:21" ht="83.4" customHeight="1">
-      <c r="A15" s="16" t="s">
+    <row r="14" customFormat="false" ht="83.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-    </row>
-    <row r="16" spans="1:21" ht="83.4" customHeight="1">
-      <c r="A16" s="16" t="s">
+      <c r="C14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="83.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="83.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" customHeight="1">
+      <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -1642,21 +1479,21 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75" customHeight="1">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -1673,31 +1510,31 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
-    <row r="19" spans="1:19" ht="15.75" customHeight="1">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>148</v>
+      <c r="I19" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="3"/>
@@ -1708,21 +1545,21 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
     </row>
-    <row r="20" spans="1:19" ht="15.75" customHeight="1">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -1739,33 +1576,33 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
-    <row r="21" spans="1:19" ht="15.75" customHeight="1">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>205</v>
+        <v>64</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>206</v>
+        <v>65</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>208</v>
+        <v>67</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
-        <v>209</v>
+        <v>68</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>210</v>
+        <v>69</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>211</v>
+        <v>70</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="3"/>
@@ -1776,21 +1613,21 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
     </row>
-    <row r="22" spans="1:19" ht="15.75" customHeight="1">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1807,12 +1644,12 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
-    <row r="23" spans="1:19" ht="15.75" customHeight="1">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -1832,23 +1669,23 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
-    <row r="24" spans="1:19" ht="15.75" customHeight="1">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -1863,21 +1700,21 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
-    <row r="25" spans="1:19" ht="15.75" customHeight="1">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1894,18 +1731,18 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
-    <row r="26" spans="1:19" ht="15.75" customHeight="1">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -1923,33 +1760,33 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row r="27" spans="1:19" ht="15.75" customHeight="1">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J27" s="17" t="s">
-        <v>168</v>
+        <v>89</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>171</v>
+        <v>91</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="3"/>
@@ -1960,33 +1797,33 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
-    <row r="28" spans="1:19" ht="15.75" customHeight="1">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3" t="s">
-        <v>167</v>
+        <v>95</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="3"/>
@@ -1997,12 +1834,12 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" spans="1:19" ht="15.75" customHeight="1">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2011,31 +1848,31 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
-      <c r="L29" s="18" t="s">
-        <v>186</v>
+      <c r="L29" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -2053,18 +1890,18 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
-    <row r="31" spans="1:19" ht="15.75" customHeight="1">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -2082,33 +1919,33 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
-    <row r="32" spans="1:19" ht="15.75" customHeight="1">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="3"/>
@@ -2119,33 +1956,33 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="3"/>
@@ -2156,12 +1993,12 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -2172,8 +2009,8 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
-      <c r="L34" s="18" t="s">
-        <v>187</v>
+      <c r="L34" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -2183,18 +2020,18 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>184</v>
+        <v>121</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2212,48 +2049,48 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
     </row>
-    <row r="36" spans="1:26" ht="36" customHeight="1">
+    <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>182</v>
+        <v>123</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-    </row>
-    <row r="37" spans="1:26" ht="36" customHeight="1">
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10"/>
+      <c r="V36" s="10"/>
+      <c r="W36" s="10"/>
+      <c r="X36" s="10"/>
+      <c r="Y36" s="10"/>
+      <c r="Z36" s="10"/>
+    </row>
+    <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E37" s="3"/>
       <c r="G37" s="3"/>
@@ -2262,7 +2099,7 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
@@ -2270,12 +2107,12 @@
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
     </row>
-    <row r="38" spans="1:26" ht="36" customHeight="1">
+    <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2285,7 +2122,7 @@
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>189</v>
+        <v>128</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
@@ -2293,12 +2130,12 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="36" customHeight="1">
+    <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2308,7 +2145,7 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
@@ -2316,18 +2153,18 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
     </row>
-    <row r="40" spans="1:26" ht="36" customHeight="1">
+    <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -2343,18 +2180,18 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
     </row>
-    <row r="41" spans="1:26" ht="36" customHeight="1">
+    <row r="41" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>158</v>
+        <v>135</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -2370,18 +2207,18 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
     </row>
-    <row r="42" spans="1:26" ht="36" customHeight="1">
+    <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>160</v>
+      <c r="D42" s="7" t="s">
+        <v>139</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -2397,15 +2234,15 @@
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
     </row>
-    <row r="43" spans="1:26" ht="36" customHeight="1">
+    <row r="43" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="8"/>
+      <c r="D43" s="7"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2420,23 +2257,23 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
     </row>
-    <row r="44" spans="1:26" ht="36" customHeight="1">
+    <row r="44" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>59</v>
+        <v>141</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -2449,23 +2286,23 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
     </row>
-    <row r="45" spans="1:26" ht="36" customHeight="1">
+    <row r="45" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>123</v>
+        <v>145</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>146</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -2478,21 +2315,21 @@
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
     </row>
-    <row r="46" spans="1:26" ht="36" customHeight="1">
+    <row r="46" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>63</v>
+        <v>149</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -2507,35 +2344,35 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
     </row>
-    <row r="47" spans="1:26" ht="23.2" customHeight="1">
+    <row r="47" customFormat="false" ht="23.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>127</v>
+        <v>152</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>153</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
@@ -2544,35 +2381,35 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
     </row>
-    <row r="48" spans="1:26" ht="36" customHeight="1">
+    <row r="48" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>129</v>
+        <v>159</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>160</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
@@ -2581,23 +2418,23 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
     </row>
-    <row r="49" spans="1:21" ht="36" customHeight="1">
+    <row r="49" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="9"/>
+      <c r="D49" s="12"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
-      <c r="L49" s="8" t="s">
-        <v>199</v>
+      <c r="L49" s="7" t="s">
+        <v>165</v>
       </c>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
@@ -2605,22 +2442,22 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
     </row>
-    <row r="50" spans="1:21" ht="36" customHeight="1">
+    <row r="50" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>196</v>
+        <v>167</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -2633,22 +2470,22 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
     </row>
-    <row r="51" spans="1:21" ht="36" customHeight="1">
+    <row r="51" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
@@ -2662,20 +2499,20 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
     </row>
-    <row r="52" spans="1:21" ht="36" customHeight="1">
+    <row r="52" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="9" t="s">
-        <v>71</v>
+      <c r="D52" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>70</v>
+        <v>173</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
@@ -2689,17 +2526,17 @@
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
     </row>
-    <row r="53" spans="1:21" ht="36" customHeight="1">
+    <row r="53" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="C53" s="3"/>
-      <c r="D53" s="9"/>
+      <c r="D53" s="12"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="10"/>
+      <c r="F53" s="13"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -2712,18 +2549,18 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
     </row>
-    <row r="54" spans="1:21" ht="36" customHeight="1">
+    <row r="54" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>213</v>
+        <v>175</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -2739,22 +2576,20 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
     </row>
-    <row r="55" spans="1:21" ht="36" customHeight="1">
+    <row r="55" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>43</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
@@ -2768,16 +2603,22 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
     </row>
-    <row r="56" spans="1:21" ht="36" customHeight="1">
+    <row r="56" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="3"/>
+        <v>180</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
@@ -2791,11 +2632,15 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
     </row>
-    <row r="57" spans="1:21" ht="36" customHeight="1">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="9"/>
+    <row r="57" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
@@ -2810,11 +2655,11 @@
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
     </row>
-    <row r="58" spans="1:21" ht="36" customHeight="1">
+    <row r="58" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="9"/>
+      <c r="D58" s="12"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
@@ -2829,14 +2674,14 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
     </row>
-    <row r="59" spans="1:21" ht="36" customHeight="1">
+    <row r="59" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="3"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="12"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
@@ -2847,17 +2692,15 @@
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
-      <c r="R59" s="3"/>
-      <c r="S59" s="7"/>
-    </row>
-    <row r="60" spans="1:21" ht="36" customHeight="1">
+    </row>
+    <row r="60" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="9"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -2868,14 +2711,16 @@
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="1:21" ht="36" customHeight="1">
+      <c r="R60" s="3"/>
+      <c r="S60" s="11"/>
+    </row>
+    <row r="61" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="9"/>
+      <c r="D61" s="12"/>
       <c r="E61" s="3"/>
-      <c r="F61" s="10"/>
+      <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -2888,13 +2733,13 @@
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
     </row>
-    <row r="62" spans="1:21" ht="36" customHeight="1">
+    <row r="62" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="9"/>
+      <c r="D62" s="12"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
+      <c r="F62" s="13"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -2907,13 +2752,13 @@
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
     </row>
-    <row r="63" spans="1:21" ht="36" customHeight="1">
+    <row r="63" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="12"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="10"/>
+      <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -2925,16 +2770,14 @@
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
       <c r="Q63" s="3"/>
-      <c r="T63" s="12"/>
-      <c r="U63" s="12"/>
-    </row>
-    <row r="64" spans="1:21" ht="36" customHeight="1">
+    </row>
+    <row r="64" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="9"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
+      <c r="F64" s="13"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -2946,14 +2789,16 @@
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="1:19" ht="36" customHeight="1">
+      <c r="T64" s="8"/>
+      <c r="U64" s="8"/>
+    </row>
+    <row r="65" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="9"/>
+      <c r="D65" s="12"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="10"/>
+      <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -2966,13 +2811,13 @@
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
     </row>
-    <row r="66" spans="1:19" ht="36" customHeight="1">
+    <row r="66" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="9"/>
+      <c r="D66" s="12"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="13"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
@@ -2985,11 +2830,11 @@
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
     </row>
-    <row r="67" spans="1:19" ht="36" customHeight="1">
+    <row r="67" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="9"/>
+      <c r="D67" s="12"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -3004,9 +2849,11 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
     </row>
-    <row r="68" spans="1:19" ht="36" customHeight="1">
+    <row r="68" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="12"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -3021,28 +2868,24 @@
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
     </row>
-    <row r="69" spans="1:19">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
-    </row>
-    <row r="70" spans="1:19">
+    <row r="69" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3063,7 +2906,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3084,7 +2927,7 @@
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3105,7 +2948,7 @@
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3126,7 +2969,7 @@
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3147,7 +2990,7 @@
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3168,7 +3011,7 @@
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3189,13 +3032,13 @@
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="13"/>
+      <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -3210,13 +3053,13 @@
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
+      <c r="F78" s="16"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -3231,7 +3074,7 @@
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3252,7 +3095,7 @@
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3273,7 +3116,7 @@
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3294,7 +3137,7 @@
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3315,7 +3158,7 @@
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3336,7 +3179,7 @@
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
     </row>
-    <row r="84" spans="1:19" ht="15.75" customHeight="1">
+    <row r="84" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3357,7 +3200,7 @@
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
     </row>
-    <row r="85" spans="1:19" ht="15.75" customHeight="1">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3378,7 +3221,7 @@
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
     </row>
-    <row r="86" spans="1:19" ht="15.75" customHeight="1">
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3399,7 +3242,7 @@
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
     </row>
-    <row r="87" spans="1:19" ht="15.75" customHeight="1">
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3420,7 +3263,7 @@
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
     </row>
-    <row r="88" spans="1:19" ht="15.75" customHeight="1">
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3441,7 +3284,7 @@
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
     </row>
-    <row r="89" spans="1:19" ht="15.75" customHeight="1">
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3462,7 +3305,7 @@
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
     </row>
-    <row r="90" spans="1:19" ht="15.75" customHeight="1">
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3483,7 +3326,7 @@
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
     </row>
-    <row r="91" spans="1:19" ht="15.75" customHeight="1">
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3504,7 +3347,7 @@
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
     </row>
-    <row r="92" spans="1:19" ht="15.75" customHeight="1">
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3525,10 +3368,10 @@
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
     </row>
-    <row r="93" spans="1:19" ht="15.75" customHeight="1">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
-      <c r="C93" s="3"/>
+      <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
@@ -3546,11 +3389,11 @@
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
     </row>
-    <row r="94" spans="1:19" ht="15.75" customHeight="1">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="3"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -3567,18 +3410,18 @@
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
     </row>
-    <row r="95" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A95" s="3"/>
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1"/>
       <c r="B95" s="3"/>
       <c r="C95" s="1"/>
       <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
+      <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
@@ -3588,18 +3431,18 @@
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
     </row>
-    <row r="96" spans="1:19" ht="15.75" customHeight="1">
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
+      <c r="C96" s="1"/>
       <c r="D96" s="3"/>
-      <c r="E96" s="1"/>
+      <c r="E96" s="3"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
-      <c r="K96" s="1"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
@@ -3609,11 +3452,11 @@
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
     </row>
-    <row r="97" spans="1:19" ht="15.75" customHeight="1">
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
@@ -3630,9 +3473,9 @@
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
     </row>
-    <row r="98" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
@@ -3651,7 +3494,7 @@
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
     </row>
-    <row r="99" spans="1:19" ht="15.75" customHeight="1">
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3672,7 +3515,7 @@
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
     </row>
-    <row r="100" spans="1:19" ht="15.75" customHeight="1">
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3693,7 +3536,7 @@
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
     </row>
-    <row r="101" spans="1:19" ht="15.75" customHeight="1">
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3714,7 +3557,7 @@
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
     </row>
-    <row r="102" spans="1:19" ht="15.75" customHeight="1">
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3735,7 +3578,7 @@
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
     </row>
-    <row r="103" spans="1:19" ht="15.75" customHeight="1">
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3756,7 +3599,7 @@
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
     </row>
-    <row r="104" spans="1:19" ht="15.75" customHeight="1">
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3777,7 +3620,7 @@
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
     </row>
-    <row r="105" spans="1:19" ht="15.75" customHeight="1">
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3798,7 +3641,7 @@
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
     </row>
-    <row r="106" spans="1:19" ht="15.75" customHeight="1">
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3819,7 +3662,7 @@
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
     </row>
-    <row r="107" spans="1:19" ht="15.75" customHeight="1">
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3840,245 +3683,287 @@
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
     </row>
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+      <c r="N108" s="1"/>
+      <c r="O108" s="1"/>
+      <c r="P108" s="1"/>
+      <c r="Q108" s="1"/>
+      <c r="R108" s="1"/>
+      <c r="S108" s="1"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="35.54296875" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" customWidth="1"/>
-    <col min="3" max="3" width="33.1328125" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A3" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>89</v>
+        <v>202</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>90</v>
+        <v>203</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>93</v>
+        <v>206</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="54.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.31640625" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="12.9" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="C2" s="15" t="str">
-        <f ca="1">TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
-        <v>2021-10-25 18-28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" t="s">
-        <v>101</v>
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="18" t="str">
+        <f aca="true">TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
+        <v>2021-11-04  14-33</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/forms/app/chv_youth_peer_education.xlsx
+++ b/forms/app/chv_youth_peer_education.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="215">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -648,22 +648,16 @@
     <t xml:space="preserve">age_group</t>
   </si>
   <si>
-    <t xml:space="preserve">age_10_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age_14_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age_17_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-19</t>
+    <t xml:space="preserve">Age_10_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age_15_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-19</t>
   </si>
   <si>
     <t xml:space="preserve">form_title</t>
@@ -979,7 +973,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z108"/>
-  <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.55078125" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.1"/>
@@ -3720,8 +3714,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D1048576"/>
+  <sheetFormatPr defaultColWidth="14.55078125" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.27"/>
@@ -3841,18 +3835,10 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
@@ -3890,12 +3876,7 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -3913,7 +3894,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="14.53515625" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.55078125" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.32"/>
@@ -3921,40 +3902,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="D1" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="E1" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="F1" s="0" t="s">
         <v>210</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C2" s="18" t="str">
         <f aca="true">TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
-        <v>2021-11-04  14-33</v>
+        <v>2022-06-06  15-11</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/forms/app/chv_youth_peer_education.xlsx
+++ b/forms/app/chv_youth_peer_education.xlsx
@@ -1,141 +1,137 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet state="visible" name="survey" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="choices" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="settings" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext uri="GoogleSheetsCustomDataVersion1">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataSignature="AMtx7mjwEIOTpwB6N+NNriffcy6zo9+06g=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="215">
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">label::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">label::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relevant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">appearance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">read_only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">constraint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">constraint_message::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">constraint_message::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calculation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice_filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hint::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hint::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">default</t>
-  </si>
-  <si>
-    <t xml:space="preserve">repeat_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media::image::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media::image::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media::audio::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media::audio::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">begin group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO_LABEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact ID of the logged in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">facility_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facility ID for the parent user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of the logged in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">db:person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">db-object</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="215">
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>label::en</t>
+  </si>
+  <si>
+    <t>label::sw</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
+    <t>media::image::en</t>
+  </si>
+  <si>
+    <t>media::image::sw</t>
+  </si>
+  <si>
+    <t>media::audio::en</t>
+  </si>
+  <si>
+    <t>media::audio::sw</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>contact_id</t>
+  </si>
+  <si>
+    <t>Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t>facility_id</t>
+  </si>
+  <si>
+    <t>Facility ID for the parent user</t>
+  </si>
+  <si>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
+    <t>end group</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>db:person</t>
+  </si>
+  <si>
+    <t>_id</t>
+  </si>
+  <si>
+    <t>db-object</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>end</t>
   </si>
   <si>
     <t xml:space="preserve">end group </t>
@@ -144,19 +140,19 @@
     <t xml:space="preserve">begin group </t>
   </si>
   <si>
-    <t xml:space="preserve">covid19_intro</t>
+    <t>covid19_intro</t>
   </si>
   <si>
     <t xml:space="preserve">Precautionary measures when visiting a client  </t>
   </si>
   <si>
-    <t xml:space="preserve">Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">covid19_intro_note</t>
+    <t>Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>covid19_intro_note</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV, you are responsible for making sure that you are providing the community with health education and services while trying to take precautions to stop the transmission of Corona virus to one another. Therefore, make sure you consider the following while you conduct the visits:  
@@ -183,28 +179,28 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">meeting_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">field-list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peer_name</t>
+    <t>meeting_info</t>
+  </si>
+  <si>
+    <t>field-list</t>
+  </si>
+  <si>
+    <t>peer_name</t>
   </si>
   <si>
     <t xml:space="preserve">Name of youth peer educator </t>
   </si>
   <si>
-    <t xml:space="preserve">Jina la M/rika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peer_phone</t>
+    <t>Jina la M/rika</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>peer_phone</t>
   </si>
   <si>
     <t xml:space="preserve">Peer Educator phone number </t>
@@ -213,31 +209,31 @@
     <t xml:space="preserve">Nambari ya simu ya M/rika </t>
   </si>
   <si>
-    <t xml:space="preserve">regex(.,'^[0oO][0-9oO]{9}$')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use the following format 0XXXXXXXXX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tumia mfumo huu 0XXXXXXXXX.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shehia</t>
+    <t>regex(.,'^[0oO][0-9oO]{9}$')</t>
+  </si>
+  <si>
+    <t>Use the following format 0XXXXXXXXX</t>
+  </si>
+  <si>
+    <t>Tumia mfumo huu 0XXXXXXXXX.</t>
+  </si>
+  <si>
+    <t>shehia</t>
   </si>
   <si>
     <t xml:space="preserve">Shehia name </t>
   </si>
   <si>
-    <t xml:space="preserve">Jina la shehia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visit_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter visit date</t>
+    <t>Jina la shehia</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>visit_date</t>
+  </si>
+  <si>
+    <t>Enter visit date</t>
   </si>
   <si>
     <t xml:space="preserve">Ingiza tarehe ya mkutano </t>
@@ -249,25 +245,25 @@
     <t xml:space="preserve"> . &lt;= date-time(decimal-date-time(today()))</t>
   </si>
   <si>
-    <t xml:space="preserve">Meeting date cannot be in the future</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tarehe ya mkutano haiwezi kuzidi tarehe ya leo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meeting_topic</t>
+    <t>Meeting date cannot be in the future</t>
+  </si>
+  <si>
+    <t>Tarehe ya mkutano haiwezi kuzidi tarehe ya leo</t>
+  </si>
+  <si>
+    <t>meeting_topic</t>
   </si>
   <si>
     <t xml:space="preserve">Meeting topic </t>
   </si>
   <si>
-    <t xml:space="preserve">Mada ya Mkutano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">youth_count_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count of youth registered, attended, and not attended</t>
+    <t>Mada ya Mkutano</t>
+  </si>
+  <si>
+    <t>youth_count_info</t>
+  </si>
+  <si>
+    <t>Count of youth registered, attended, and not attended</t>
   </si>
   <si>
     <t xml:space="preserve">Idadi ya vijana waliosajiliwa, waliyoshirikia na wasiyoshiriki </t>
@@ -291,22 +287,22 @@
     <t xml:space="preserve">youth_registered_note </t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Number of registered youth in the groups &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Idadi ya vijana waliosajiliwa katika vikundi&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">male_registered</t>
+    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Number of registered youth in the groups &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Idadi ya vijana waliosajiliwa katika vikundi&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>male_registered</t>
   </si>
   <si>
     <t xml:space="preserve">Count of registered male </t>
   </si>
   <si>
-    <t xml:space="preserve">Idadi ya wanaume</t>
+    <t>Idadi ya wanaume</t>
   </si>
   <si>
     <t xml:space="preserve">. &gt; 0 </t>
@@ -315,37 +311,37 @@
     <t xml:space="preserve">Number of registered male should be greater than 0 </t>
   </si>
   <si>
-    <t xml:space="preserve">Idadi ya wanaume walisajiliwa iwe zaidi ya 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">female_registered</t>
+    <t>Idadi ya wanaume walisajiliwa iwe zaidi ya 0</t>
+  </si>
+  <si>
+    <t>female_registered</t>
   </si>
   <si>
     <t xml:space="preserve">Count of registered female </t>
   </si>
   <si>
-    <t xml:space="preserve">Idadi ya wanawake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">. &gt; 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of registered female should be greater than 0</t>
+    <t>Idadi ya wanawake</t>
+  </si>
+  <si>
+    <t>. &gt; 0</t>
+  </si>
+  <si>
+    <t>Number of registered female should be greater than 0</t>
   </si>
   <si>
     <t xml:space="preserve">Idadi ya wanawake waliosajiliwa iwe zaidi ya 0 </t>
   </si>
   <si>
-    <t xml:space="preserve">calculate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_registered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${male_registered}="" or ${male_registered} &lt;= 0  or ${female_registered} = "" or ${female_registered} &lt;= 0 , 0,number(${male_registered}) + number(${female_registered}))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_registered_note</t>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>total_registered</t>
+  </si>
+  <si>
+    <t>if(${male_registered}="" or ${male_registered} &lt;= 0  or ${female_registered} = "" or ${female_registered} &lt;= 0 , 0,number(${male_registered}) + number(${female_registered}))</t>
+  </si>
+  <si>
+    <t>total_registered_note</t>
   </si>
   <si>
     <t xml:space="preserve">Total youth registered: ${total_registered} </t>
@@ -354,53 +350,53 @@
     <t xml:space="preserve">&lt;b&gt;Jumla waliyosajiliwa:&lt;/b&gt; ${total_registered} </t>
   </si>
   <si>
-    <t xml:space="preserve">youth_participated_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Number of youth participated in the meeting&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Vijana walioshiriki katika mkutano wa kikundi&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">male_attended</t>
+    <t>youth_participated_note</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Number of youth participated in the meeting&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Vijana walioshiriki katika mkutano wa kikundi&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>male_attended</t>
   </si>
   <si>
     <t xml:space="preserve">Count of male participants </t>
   </si>
   <si>
-    <t xml:space="preserve">number(${male_attended}) &lt;= number(${male_registered}) and number(${male_attended}) &gt;= 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male attended cannot be greater than male registered</t>
+    <t>number(${male_attended}) &lt;= number(${male_registered}) and number(${male_attended}) &gt;= 0</t>
+  </si>
+  <si>
+    <t>Male attended cannot be greater than male registered</t>
   </si>
   <si>
     <t xml:space="preserve">Idadi ya wanaume walioshiriki haiwezi kuwa kubwa kuliko idadi ya waliyosajiliwa </t>
   </si>
   <si>
-    <t xml:space="preserve">female_attended</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count of female participants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number(${female_attended}) &lt;= number(${female_registered}) and number(${female_attended}) &gt;= 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female attended cannot be greater than female registered</t>
+    <t>female_attended</t>
+  </si>
+  <si>
+    <t>Count of female participants</t>
+  </si>
+  <si>
+    <t>number(${female_attended}) &lt;= number(${female_registered}) and number(${female_attended}) &gt;= 0</t>
+  </si>
+  <si>
+    <t>Female attended cannot be greater than female registered</t>
   </si>
   <si>
     <t xml:space="preserve">Idadi ya wanawake walioshiriki haiwezi kuwa kubwa kuliko idadi ya wanawake waliyosajiliwa </t>
   </si>
   <si>
-    <t xml:space="preserve">total_attended</t>
+    <t>total_attended</t>
   </si>
   <si>
     <t xml:space="preserve">if(${male_attended}="" or ${male_attended} &lt; 0  or ${female_attended} = "" or ${female_attended} &lt;= 0 , 0,number(${male_attended}) + number(${female_attended}))
 </t>
   </si>
   <si>
-    <t xml:space="preserve">total_attended_note</t>
+    <t>total_attended_note</t>
   </si>
   <si>
     <t xml:space="preserve">Total youth participants: ${total_attended} </t>
@@ -412,49 +408,49 @@
     <t xml:space="preserve">youth_not_attended_note </t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Number of youth not attend a the meeting&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#337ab7;font-style: italic"&gt;Idadi ya vijana wasiohudhuria katika mkutano wa vikundi&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">male_absentees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${male_registered}="" or ${male_registered} &lt;= 0  or ${male_attended} = "" or ${male_attended} &lt; 0 , 0,number(${male_registered})-number(${male_attended}))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">female_absentees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${female_registered}="" or ${female_registered} &lt;= 0  or ${female_attended} = "" or ${female_attended} &lt; 0 , 0,number(${female_registered})-number(${female_attended}))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_absentees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number(${male_absentees})+ number(${female_absentees})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">male_absentees_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Count of male absentees:&lt;/b&gt; ${male_absentees}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Idadi ya wanaume wasiyohudhuria:&lt;/b&gt; ${male_absentees}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">female_absentees_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Count of female absentees:&lt;/b&gt; ${female_absentees}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Idadi ya wanawake wasiyohudhuria:&lt;/b&gt; ${female_absentees}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_absentees_note</t>
+    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Number of youth not attend a the meeting&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#337ab7;font-style: italic"&gt;Idadi ya vijana wasiohudhuria katika mkutano wa vikundi&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>male_absentees</t>
+  </si>
+  <si>
+    <t>if(${male_registered}="" or ${male_registered} &lt;= 0  or ${male_attended} = "" or ${male_attended} &lt; 0 , 0,number(${male_registered})-number(${male_attended}))</t>
+  </si>
+  <si>
+    <t>female_absentees</t>
+  </si>
+  <si>
+    <t>if(${female_registered}="" or ${female_registered} &lt;= 0  or ${female_attended} = "" or ${female_attended} &lt; 0 , 0,number(${female_registered})-number(${female_attended}))</t>
+  </si>
+  <si>
+    <t>total_absentees</t>
+  </si>
+  <si>
+    <t>number(${male_absentees})+ number(${female_absentees})</t>
+  </si>
+  <si>
+    <t>male_absentees_note</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Count of male absentees:&lt;/b&gt; ${male_absentees}</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Idadi ya wanaume wasiyohudhuria:&lt;/b&gt; ${male_absentees}</t>
+  </si>
+  <si>
+    <t>female_absentees_note</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Count of female absentees:&lt;/b&gt; ${female_absentees}</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Idadi ya wanawake wasiyohudhuria:&lt;/b&gt; ${female_absentees}</t>
+  </si>
+  <si>
+    <t>total_absentees_note</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;b&gt;Total absentees:&lt;/b&gt; ${total_absentees} </t>
@@ -463,19 +459,19 @@
     <t xml:space="preserve">&lt;b&gt;Jumla wasiyohudhuria:&lt;/b&gt; ${total_absentees} </t>
   </si>
   <si>
-    <t xml:space="preserve">meeting_challenges</t>
+    <t>meeting_challenges</t>
   </si>
   <si>
     <t xml:space="preserve">Challenges encountered in the group meeting </t>
   </si>
   <si>
-    <t xml:space="preserve">Changamoto zilizojitokeza katika mkutano wa kikundi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">multiline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">referral_info</t>
+    <t>Changamoto zilizojitokeza katika mkutano wa kikundi</t>
+  </si>
+  <si>
+    <t>multiline</t>
+  </si>
+  <si>
+    <t>referral_info</t>
   </si>
   <si>
     <t xml:space="preserve">Youth Referral </t>
@@ -484,16 +480,16 @@
     <t xml:space="preserve">Rufaa ya vijana </t>
   </si>
   <si>
-    <t xml:space="preserve">select_one yes_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has_given_referral_this_month</t>
+    <t>select_one yes_no</t>
+  </si>
+  <si>
+    <t>has_given_referral_this_month</t>
   </si>
   <si>
     <t xml:space="preserve">Have you given a referral to a youth in this month? </t>
   </si>
   <si>
-    <t xml:space="preserve">Je umewahi kutoa rufaa kwa kijana ndani ya mwezi huu?</t>
+    <t>Je umewahi kutoa rufaa kwa kijana ndani ya mwezi huu?</t>
   </si>
   <si>
     <t xml:space="preserve"> referral_received_per_month</t>
@@ -502,57 +498,57 @@
     <t xml:space="preserve">Referrals given this month </t>
   </si>
   <si>
-    <t xml:space="preserve">Idadi ya rufaa ulizotoa kwenye mwezi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${has_given_referral_this_month}=”yes”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.&gt;=0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referral count should be greater or equal to 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">idadi haiwezi kuwa chini ya 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">facility_referral_count</t>
+    <t>Idadi ya rufaa ulizotoa kwenye mwezi</t>
+  </si>
+  <si>
+    <t>${has_given_referral_this_month}=”yes”</t>
+  </si>
+  <si>
+    <t>.&gt;=0</t>
+  </si>
+  <si>
+    <t>Referral count should be greater or equal to 0</t>
+  </si>
+  <si>
+    <t>idadi haiwezi kuwa chini ya 0</t>
+  </si>
+  <si>
+    <t>facility_referral_count</t>
   </si>
   <si>
     <t xml:space="preserve">Out of those, how many referrals were directed to health facility? </t>
   </si>
   <si>
-    <t xml:space="preserve">Kati ya hizo ni rufaa ngapi uliziwasilisha  kituo cha Afya?</t>
+    <t>Kati ya hizo ni rufaa ngapi uliziwasilisha  kituo cha Afya?</t>
   </si>
   <si>
     <t xml:space="preserve"> number(${facility_referral_count}) &lt;= number(${referral_received_per_month})  and number(${facility_referral_count})  &gt;= 0</t>
   </si>
   <si>
-    <t xml:space="preserve">Facility referral should be between 0 and total referrals</t>
+    <t>Facility referral should be between 0 and total referrals</t>
   </si>
   <si>
     <t xml:space="preserve">Idadi ya rufaa za kituo cha afya haiwezi  iwe baina ya 0 na jumla ya idadi za rufaa za mwezi </t>
   </si>
   <si>
-    <t xml:space="preserve">parental_referral_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if(${referral_received_per_month}="" or ${referral_received_per_month} &lt; 0  or ${facility_referral_count} = "" or ${facility_referral_count} &lt; 0 or 
+    <t>parental_referral_count</t>
+  </si>
+  <si>
+    <t>if(${referral_received_per_month}="" or ${referral_received_per_month} &lt; 0  or ${facility_referral_count} = "" or ${facility_referral_count} &lt; 0 or 
 number(${referral_received_per_month}) - number(${facility_referral_count}) &lt; 0
  , 0, number(${referral_received_per_month}) - number(${facility_referral_count}) )</t>
   </si>
   <si>
-    <t xml:space="preserve">parental_referral_count_qn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Referrals which were directed to parents/guardians &lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;b&gt;Rufaa ulizoziunganisha kwa Walezi/wazazi wa vijana&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parental_referral_count_answer</t>
+    <t>parental_referral_count_qn</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Referrals which were directed to parents/guardians &lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Rufaa ulizoziunganisha kwa Walezi/wazazi wa vijana&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>parental_referral_count_answer</t>
   </si>
   <si>
     <t xml:space="preserve">${parental_referral_count} </t>
@@ -561,10 +557,10 @@
     <t xml:space="preserve">educate_youth_educator </t>
   </si>
   <si>
-    <t xml:space="preserve">Msisitize Muelimishe rika na vijana kujenga Utayari na vijana kutoa taarifa juu ya changamoto zinazowakabili</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${has_given_referral_this_month}=”no”</t>
+    <t>Msisitize Muelimishe rika na vijana kujenga Utayari na vijana kutoa taarifa juu ya changamoto zinazowakabili</t>
+  </si>
+  <si>
+    <t>${has_given_referral_this_month}=”no”</t>
   </si>
   <si>
     <t xml:space="preserve">chv_attendance </t>
@@ -576,16 +572,16 @@
     <t xml:space="preserve">Mahudhurio ya mkutano </t>
   </si>
   <si>
-    <t xml:space="preserve">note_chv_attend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:red;font-style: italic"&gt;To be answered by the CHV &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="display:block;color:red;font-style: italic;padding-left:1em"&gt;Usimsomee, jaza wewe (CHV). &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">did_chv_attend</t>
+    <t>note_chv_attend</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:red;font-style: italic"&gt;To be answered by the CHV &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;color:red;font-style: italic;padding-left:1em"&gt;Usimsomee, jaza wewe (CHV). &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>did_chv_attend</t>
   </si>
   <si>
     <t xml:space="preserve">Did you attend the meeting? </t>
@@ -594,167 +590,142 @@
     <t xml:space="preserve">Je ulihudhuria mkutano? </t>
   </si>
   <si>
-    <t xml:space="preserve">list_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ndiyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hapana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">health_concerns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cleanliness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleanliness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usafi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">environment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mazingira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age_group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age_10_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age_15_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">form_title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">form_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance_name</t>
+    <t>list_name</t>
+  </si>
+  <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Ndiyo</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Hapana</t>
+  </si>
+  <si>
+    <t>health_concerns</t>
+  </si>
+  <si>
+    <t>cleanliness</t>
+  </si>
+  <si>
+    <t>Cleanliness</t>
+  </si>
+  <si>
+    <t>Usafi</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Maji</t>
+  </si>
+  <si>
+    <t>environment</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Mazingira</t>
+  </si>
+  <si>
+    <t>age_group</t>
+  </si>
+  <si>
+    <t>Age_10_14</t>
+  </si>
+  <si>
+    <t>10-14</t>
+  </si>
+  <si>
+    <t>Age_15_19</t>
+  </si>
+  <si>
+    <t>15-19</t>
+  </si>
+  <si>
+    <t>form_title</t>
+  </si>
+  <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>instance_name</t>
   </si>
   <si>
     <t xml:space="preserve">Elimu Rika na Afya Uzazi </t>
   </si>
   <si>
-    <t xml:space="preserve">chv_youth_peer_education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data</t>
+    <t>chv_youth_peer_education</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="@"/>
-  </numFmts>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="7">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <sz val="10.0"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="Lato"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <name val="Sans"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1D1C1D"/>
-      <name val="Slack-Lato"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Sans"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Roboto"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -762,230 +733,326 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF8F8F8"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F8F8"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF8F8F8"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="3">
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  </cellStyleXfs>
+  <cellXfs count="16">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF8F8F8"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1D1C1D"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+  <a:themeElements>
+    <a:clrScheme name="Sheets">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="0000FF"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Sheets">
+      <a:majorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z108"/>
-  <sheetFormatPr defaultColWidth="14.55078125" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="78.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="72.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="59.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="47.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="74.54"/>
+    <col customWidth="1" min="1" max="1" width="23.25"/>
+    <col customWidth="1" min="2" max="2" width="29.13"/>
+    <col customWidth="1" min="3" max="3" width="78.25"/>
+    <col customWidth="1" min="4" max="4" width="46.25"/>
+    <col customWidth="1" min="5" max="5" width="14.5"/>
+    <col customWidth="1" min="6" max="6" width="72.13"/>
+    <col customWidth="1" min="7" max="8" width="14.5"/>
+    <col customWidth="1" min="9" max="9" width="59.0"/>
+    <col customWidth="1" min="10" max="10" width="47.38"/>
+    <col customWidth="1" min="11" max="11" width="74.5"/>
+    <col customWidth="1" min="12" max="26" width="14.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1050,7 +1117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -1062,8 +1129,8 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="4" t="n">
-        <f aca="false">FALSE()</f>
+      <c r="F2" s="4" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
       <c r="G2" s="1"/>
@@ -1080,7 +1147,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1107,7 +1174,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -1134,7 +1201,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
@@ -1161,7 +1228,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1188,7 +1255,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -1213,7 +1280,7 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
@@ -1240,7 +1307,7 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
@@ -1269,7 +1336,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -1294,7 +1361,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -1319,7 +1386,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
@@ -1344,7 +1411,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
@@ -1369,7 +1436,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="83.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="83.25" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
@@ -1396,7 +1463,7 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="83.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="83.25" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>43</v>
       </c>
@@ -1423,7 +1490,7 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="83.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="83.25" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
@@ -1446,14 +1513,16 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -1473,7 +1542,7 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1504,7 +1573,7 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>53</v>
       </c>
@@ -1521,13 +1590,13 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="K19" s="1" t="s">
         <v>59</v>
       </c>
       <c r="L19" s="5"/>
@@ -1539,7 +1608,7 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
@@ -1570,7 +1639,7 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>63</v>
       </c>
@@ -1607,7 +1676,7 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1638,7 +1707,7 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
@@ -1663,7 +1732,7 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>39</v>
       </c>
@@ -1694,7 +1763,7 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>78</v>
       </c>
@@ -1725,7 +1794,7 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>43</v>
       </c>
@@ -1754,7 +1823,7 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>85</v>
       </c>
@@ -1776,7 +1845,7 @@
       <c r="I27" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="J27" s="1" t="s">
         <v>90</v>
       </c>
       <c r="K27" s="3" t="s">
@@ -1791,7 +1860,7 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>85</v>
       </c>
@@ -1828,7 +1897,7 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>98</v>
       </c>
@@ -1848,14 +1917,14 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
-      <c r="P29" s="3" t="n">
-        <v>0</v>
+      <c r="P29" s="3">
+        <v>0.0</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>43</v>
       </c>
@@ -1884,7 +1953,7 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>43</v>
       </c>
@@ -1913,7 +1982,7 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -1950,7 +2019,7 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>85</v>
       </c>
@@ -1987,7 +2056,7 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>98</v>
       </c>
@@ -2014,7 +2083,7 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
@@ -2043,7 +2112,7 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" ht="36.0" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
@@ -2079,7 +2148,7 @@
       <c r="Y36" s="10"/>
       <c r="Z36" s="10"/>
     </row>
-    <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" ht="36.0" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>98</v>
       </c>
@@ -2101,7 +2170,7 @@
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" ht="36.0" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>98</v>
       </c>
@@ -2124,7 +2193,7 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" ht="36.0" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>98</v>
       </c>
@@ -2147,7 +2216,7 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" ht="36.0" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>43</v>
       </c>
@@ -2174,7 +2243,7 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" ht="36.0" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
@@ -2201,7 +2270,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" ht="36.0" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>43</v>
       </c>
@@ -2228,7 +2297,7 @@
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" ht="36.0" customHeight="1">
       <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
@@ -2251,7 +2320,7 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" ht="36.0" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>53</v>
       </c>
@@ -2280,7 +2349,7 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" ht="36.0" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>21</v>
       </c>
@@ -2309,7 +2378,7 @@
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" ht="36.0" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>147</v>
       </c>
@@ -2338,7 +2407,7 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="23.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
         <v>85</v>
       </c>
@@ -2375,7 +2444,7 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" ht="36.0" customHeight="1">
       <c r="A48" s="3" t="s">
         <v>85</v>
       </c>
@@ -2412,7 +2481,7 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" ht="36.0" customHeight="1">
       <c r="A49" s="3" t="s">
         <v>98</v>
       </c>
@@ -2436,7 +2505,7 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" ht="36.0" customHeight="1">
       <c r="A50" s="3" t="s">
         <v>43</v>
       </c>
@@ -2464,7 +2533,7 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" ht="36.0" customHeight="1">
       <c r="A51" s="3" t="s">
         <v>43</v>
       </c>
@@ -2493,7 +2562,7 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" ht="36.0" customHeight="1">
       <c r="A52" s="3" t="s">
         <v>43</v>
       </c>
@@ -2520,7 +2589,7 @@
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" ht="36.0" customHeight="1">
       <c r="A53" s="3" t="s">
         <v>31</v>
       </c>
@@ -2530,7 +2599,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="12"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="13"/>
+      <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -2543,7 +2612,7 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" ht="36.0" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>39</v>
       </c>
@@ -2570,17 +2639,17 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" ht="36.0" customHeight="1">
       <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="13" t="s">
         <v>179</v>
       </c>
       <c r="E55" s="3"/>
@@ -2597,7 +2666,7 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" ht="36.0" customHeight="1">
       <c r="A56" s="3" t="s">
         <v>147</v>
       </c>
@@ -2626,15 +2695,15 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" ht="36.0" customHeight="1">
       <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
@@ -2649,7 +2718,7 @@
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" ht="36.0" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2668,10 +2737,10 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" ht="36.0" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
-      <c r="C59" s="14"/>
+      <c r="C59" s="13"/>
       <c r="D59" s="12"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -2687,14 +2756,14 @@
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" ht="36.0" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
-      <c r="C60" s="13"/>
+      <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -2708,7 +2777,7 @@
       <c r="R60" s="3"/>
       <c r="S60" s="11"/>
     </row>
-    <row r="61" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" ht="36.0" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2727,13 +2796,13 @@
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" ht="36.0" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="12"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="13"/>
+      <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -2746,7 +2815,7 @@
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" ht="36.0" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -2765,13 +2834,13 @@
       <c r="P63" s="3"/>
       <c r="Q63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" ht="36.0" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="13"/>
+      <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -2783,10 +2852,10 @@
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
-      <c r="T64" s="8"/>
-      <c r="U64" s="8"/>
-    </row>
-    <row r="65" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T64" s="1"/>
+      <c r="U64" s="1"/>
+    </row>
+    <row r="65" ht="36.0" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2805,13 +2874,13 @@
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" ht="36.0" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="12"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="13"/>
+      <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
@@ -2824,7 +2893,7 @@
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" ht="36.0" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -2843,7 +2912,7 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" ht="36.0" customHeight="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -2862,7 +2931,7 @@
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" ht="36.0" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="E69" s="3"/>
@@ -2879,7 +2948,7 @@
       <c r="P69" s="3"/>
       <c r="Q69" s="3"/>
     </row>
-    <row r="70" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2900,7 +2969,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
     </row>
-    <row r="71" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2921,7 +2990,7 @@
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
     </row>
-    <row r="72" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" ht="12.75" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2942,7 +3011,7 @@
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
     </row>
-    <row r="73" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2963,7 +3032,7 @@
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
     </row>
-    <row r="74" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2984,7 +3053,7 @@
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3005,7 +3074,7 @@
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
     </row>
-    <row r="76" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3026,7 +3095,7 @@
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
     </row>
-    <row r="77" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3047,13 +3116,13 @@
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
     </row>
-    <row r="78" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="16"/>
+      <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -3068,7 +3137,7 @@
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
     </row>
-    <row r="79" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3089,7 +3158,7 @@
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
     </row>
-    <row r="80" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3110,7 +3179,7 @@
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
     </row>
-    <row r="81" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" ht="12.75" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3131,7 +3200,7 @@
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
     </row>
-    <row r="82" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3152,7 +3221,7 @@
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
     </row>
-    <row r="83" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" ht="12.75" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3173,7 +3242,7 @@
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
     </row>
-    <row r="84" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" ht="12.75" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3194,7 +3263,7 @@
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
     </row>
-    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3215,7 +3284,7 @@
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
     </row>
-    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3236,7 +3305,7 @@
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
     </row>
-    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3257,7 +3326,7 @@
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
     </row>
-    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3278,7 +3347,7 @@
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
     </row>
-    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3299,7 +3368,7 @@
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
     </row>
-    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3320,7 +3389,7 @@
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
     </row>
-    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3341,7 +3410,7 @@
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
     </row>
-    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3362,7 +3431,7 @@
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
     </row>
-    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3383,7 +3452,7 @@
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
     </row>
-    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="3"/>
@@ -3404,7 +3473,7 @@
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
     </row>
-    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="3"/>
       <c r="C95" s="1"/>
@@ -3425,7 +3494,7 @@
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
     </row>
-    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="1"/>
@@ -3446,7 +3515,7 @@
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
     </row>
-    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -3467,7 +3536,7 @@
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
     </row>
-    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="1"/>
@@ -3488,7 +3557,7 @@
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
     </row>
-    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3509,7 +3578,7 @@
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
     </row>
-    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3530,7 +3599,7 @@
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
     </row>
-    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3551,7 +3620,7 @@
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
     </row>
-    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3572,7 +3641,7 @@
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3593,7 +3662,7 @@
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
     </row>
-    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3614,7 +3683,7 @@
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
     </row>
-    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3635,7 +3704,7 @@
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
     </row>
-    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3656,7 +3725,7 @@
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
     </row>
-    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3677,7 +3746,7 @@
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
     </row>
-    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3698,115 +3767,1004 @@
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
     </row>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="14.55078125" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.14"/>
+    <col customWidth="1" min="1" max="1" width="35.5"/>
+    <col customWidth="1" min="2" max="2" width="18.25"/>
+    <col customWidth="1" min="3" max="3" width="33.13"/>
+    <col customWidth="1" min="4" max="26" width="14.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="14" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>200</v>
       </c>
@@ -3820,7 +4778,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>200</v>
       </c>
@@ -3834,117 +4792,2093 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" ht="12.75" customHeight="1"/>
+    <row r="17" ht="12.75" customHeight="1"/>
+    <row r="18" ht="12.75" customHeight="1"/>
+    <row r="19" ht="12.75" customHeight="1"/>
+    <row r="20" ht="12.75" customHeight="1"/>
+    <row r="21" ht="12.75" customHeight="1"/>
+    <row r="22" ht="12.75" customHeight="1"/>
+    <row r="23" ht="12.75" customHeight="1"/>
+    <row r="24" ht="12.75" customHeight="1"/>
+    <row r="25" ht="12.75" customHeight="1"/>
+    <row r="26" ht="12.75" customHeight="1"/>
+    <row r="27" ht="12.75" customHeight="1"/>
+    <row r="28" ht="12.75" customHeight="1"/>
+    <row r="29" ht="12.75" customHeight="1"/>
+    <row r="30" ht="12.75" customHeight="1"/>
+    <row r="31" ht="12.75" customHeight="1"/>
+    <row r="32" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="14.55078125" defaultRowHeight="13" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.32"/>
+    <col customWidth="1" min="1" max="1" width="54.63"/>
+    <col customWidth="1" min="2" max="2" width="18.38"/>
+    <col customWidth="1" min="3" max="26" width="14.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="14" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="18" t="str">
-        <f aca="true">TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
-        <v>2022-06-06  15-11</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="15" t="str">
+        <f>TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
+        <v>2022-11-04_01-00</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="14" t="s">
         <v>214</v>
       </c>
     </row>
+    <row r="3" ht="12.75" customHeight="1"/>
+    <row r="4" ht="12.75" customHeight="1"/>
+    <row r="5" ht="12.75" customHeight="1"/>
+    <row r="6" ht="12.75" customHeight="1"/>
+    <row r="7" ht="12.75" customHeight="1"/>
+    <row r="8" ht="12.75" customHeight="1"/>
+    <row r="9" ht="12.75" customHeight="1"/>
+    <row r="10" ht="12.75" customHeight="1"/>
+    <row r="11" ht="12.75" customHeight="1"/>
+    <row r="12" ht="12.75" customHeight="1"/>
+    <row r="13" ht="12.75" customHeight="1"/>
+    <row r="14" ht="12.75" customHeight="1"/>
+    <row r="15" ht="12.75" customHeight="1"/>
+    <row r="16" ht="12.75" customHeight="1"/>
+    <row r="17" ht="12.75" customHeight="1"/>
+    <row r="18" ht="12.75" customHeight="1"/>
+    <row r="19" ht="12.75" customHeight="1"/>
+    <row r="20" ht="12.75" customHeight="1"/>
+    <row r="21" ht="12.75" customHeight="1"/>
+    <row r="22" ht="12.75" customHeight="1"/>
+    <row r="23" ht="12.75" customHeight="1"/>
+    <row r="24" ht="12.75" customHeight="1"/>
+    <row r="25" ht="12.75" customHeight="1"/>
+    <row r="26" ht="12.75" customHeight="1"/>
+    <row r="27" ht="12.75" customHeight="1"/>
+    <row r="28" ht="12.75" customHeight="1"/>
+    <row r="29" ht="12.75" customHeight="1"/>
+    <row r="30" ht="12.75" customHeight="1"/>
+    <row r="31" ht="12.75" customHeight="1"/>
+    <row r="32" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/forms/app/chv_youth_peer_education.xlsx
+++ b/forms/app/chv_youth_peer_education.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataSignature="AMtx7mjwEIOTpwB6N+NNriffcy6zo9+06g=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataSignature="AMtx7mhwNajzAWbnnBtKUQCWoeuCIfp0jA=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="215">
   <si>
     <t>type</t>
   </si>
@@ -725,7 +725,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -796,9 +795,6 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
@@ -810,6 +806,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -1520,7 +1519,7 @@
       <c r="B17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="3"/>
@@ -1911,7 +1910,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
-      <c r="L29" s="9" t="s">
+      <c r="L29" s="8" t="s">
         <v>100</v>
       </c>
       <c r="M29" s="3"/>
@@ -2072,7 +2071,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
-      <c r="L34" s="9" t="s">
+      <c r="L34" s="8" t="s">
         <v>118</v>
       </c>
       <c r="M34" s="3"/>
@@ -2122,31 +2121,31 @@
       <c r="C36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="9" t="s">
         <v>124</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="10"/>
-      <c r="S36" s="10"/>
-      <c r="T36" s="10"/>
-      <c r="U36" s="10"/>
-      <c r="V36" s="10"/>
-      <c r="W36" s="10"/>
-      <c r="X36" s="10"/>
-      <c r="Y36" s="10"/>
-      <c r="Z36" s="10"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
     </row>
     <row r="37" ht="36.0" customHeight="1">
       <c r="A37" s="3" t="s">
@@ -2359,7 +2358,7 @@
       <c r="C45" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E45" s="3"/>
@@ -2388,7 +2387,7 @@
       <c r="C46" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="11" t="s">
         <v>150</v>
       </c>
       <c r="E46" s="3" t="s">
@@ -2417,7 +2416,7 @@
       <c r="C47" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="11" t="s">
         <v>153</v>
       </c>
       <c r="E47" s="3" t="s">
@@ -2454,7 +2453,7 @@
       <c r="C48" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="11" t="s">
         <v>160</v>
       </c>
       <c r="E48" s="3" t="s">
@@ -2489,7 +2488,7 @@
         <v>164</v>
       </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="12"/>
+      <c r="D49" s="11"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -2515,7 +2514,7 @@
       <c r="C50" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="11" t="s">
         <v>168</v>
       </c>
       <c r="E50" s="3"/>
@@ -2570,7 +2569,7 @@
         <v>171</v>
       </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="11" t="s">
         <v>172</v>
       </c>
       <c r="E52" s="3"/>
@@ -2597,7 +2596,7 @@
         <v>144</v>
       </c>
       <c r="C53" s="3"/>
-      <c r="D53" s="12"/>
+      <c r="D53" s="11"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
@@ -2622,12 +2621,14 @@
       <c r="C54" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="11" t="s">
         <v>176</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
+      <c r="G54" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
@@ -2676,7 +2677,7 @@
       <c r="C56" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="11" t="s">
         <v>182</v>
       </c>
       <c r="E56" s="3" t="s">
@@ -2722,7 +2723,7 @@
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="12"/>
+      <c r="D58" s="11"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
@@ -2741,7 +2742,7 @@
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="13"/>
-      <c r="D59" s="12"/>
+      <c r="D59" s="11"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
@@ -2775,13 +2776,13 @@
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
-      <c r="S60" s="11"/>
+      <c r="S60" s="10"/>
     </row>
     <row r="61" ht="36.0" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="12"/>
+      <c r="D61" s="11"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
@@ -2800,7 +2801,7 @@
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="12"/>
+      <c r="D62" s="11"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
@@ -2819,7 +2820,7 @@
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="12"/>
+      <c r="D63" s="11"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
@@ -2859,7 +2860,7 @@
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="12"/>
+      <c r="D65" s="11"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
@@ -2878,7 +2879,7 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="12"/>
+      <c r="D66" s="11"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -2897,7 +2898,7 @@
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="12"/>
+      <c r="D67" s="11"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -2916,7 +2917,7 @@
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="12"/>
+      <c r="D68" s="11"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -5868,7 +5869,7 @@
       </c>
       <c r="C2" s="15" t="str">
         <f>TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
-        <v>2022-11-04_01-00</v>
+        <v>2023-03-07_03-39</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>213</v>
